--- a/mode_docx_gen/pmi_ka/part/lvcbsup/rcbf1/RCBF1.xlsx
+++ b/mode_docx_gen/pmi_ka/part/lvcbsup/rcbf1/RCBF1.xlsx
@@ -307,9 +307,6 @@
     <t>SGF8</t>
   </si>
   <si>
-    <t>Блокировка включения от превышения ресурса В</t>
-  </si>
-  <si>
     <t>Бл_вкл_от_прев_рес</t>
   </si>
   <si>
@@ -410,6 +407,9 @@
   </si>
   <si>
     <t>alias</t>
+  </si>
+  <si>
+    <t>Блокировка включения при превышении ресурса В</t>
   </si>
 </sst>
 </file>
@@ -925,7 +925,7 @@
         <v>29</v>
       </c>
       <c r="AE1" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2316,16 +2316,16 @@
         <v>62</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>91</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>43</v>
@@ -2408,10 +2408,10 @@
         <v>62</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>93</v>
@@ -2503,7 +2503,7 @@
         <v>86</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>56</v>
@@ -2684,10 +2684,10 @@
         <v>62</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>90</v>
@@ -2776,16 +2776,16 @@
         <v>62</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>92</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>43</v>
@@ -2868,10 +2868,10 @@
         <v>62</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>94</v>
@@ -2960,13 +2960,13 @@
         <v>62</v>
       </c>
       <c r="C24" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>55</v>
@@ -3052,22 +3052,22 @@
         <v>62</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E25" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G25" s="2" t="s">
+      <c r="H25" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="I25" s="2">
         <v>0</v>
@@ -3085,19 +3085,19 @@
         <v>63</v>
       </c>
       <c r="N25" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="O25" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="O25" s="2" t="s">
+      <c r="P25" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="R25" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="P25" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q25" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="S25" s="2" t="s">
         <v>41</v>
@@ -3127,7 +3127,7 @@
         <v>66</v>
       </c>
       <c r="AB25" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AC25" s="2" t="s">
         <v>33</v>
@@ -3136,7 +3136,7 @@
         <v>33</v>
       </c>
       <c r="AE25" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.25">
@@ -3147,22 +3147,22 @@
         <v>62</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G26" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="I26" s="2">
         <v>0</v>
@@ -3231,7 +3231,7 @@
         <v>33</v>
       </c>
       <c r="AE26" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.25">
@@ -3242,22 +3242,22 @@
         <v>62</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>116</v>
-      </c>
       <c r="F27" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G27" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="I27" s="2">
         <v>0</v>
@@ -3326,7 +3326,7 @@
         <v>33</v>
       </c>
       <c r="AE27" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -3365,7 +3365,7 @@
         <v>60</v>
       </c>
       <c r="B3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3375,15 +3375,15 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B6">
         <v>10</v>
